--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
@@ -1,24 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F042CC4DC70FDBC07EA4F789097A6BE6FA1B54D9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{29EB6B5A-F75F-4A28-BA46-C91A923FEB28}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_16">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_223">Hidden_2!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="103">
   <si>
     <t>48978</t>
   </si>
@@ -128,6 +136,9 @@
     <t>436297</t>
   </si>
   <si>
+    <t>571932</t>
+  </si>
+  <si>
     <t>436304</t>
   </si>
   <si>
@@ -221,6 +232,9 @@
     <t>Servidor(a) público(a) y/o área responsable de recibir los resultados</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Total de solventaciones y/o aclaraciones realizadas</t>
   </si>
   <si>
@@ -245,22 +259,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>A7E4E5621AE64B8A7083F9B30C9ED708</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>Del 01/01/2021 al 31/12/2021</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Auditoría externa</t>
@@ -269,31 +268,10 @@
     <t>Financiera</t>
   </si>
   <si>
-    <t>1826</t>
-  </si>
-  <si>
-    <t>Auditoria Superior de la Federación</t>
-  </si>
-  <si>
-    <t>AEGF/DSFCA/AOPS/2022-05-1033</t>
-  </si>
-  <si>
-    <t>Subisidios Federales para Organisos Descentralizados  Estatales de Educación Media Superior y Superior en su Vertiente Tecnologica, Politecnica y Pública con Apoyo Solidario (U006) de la Cuenta Pública 2021.</t>
+    <t/>
   </si>
   <si>
     <t>Ejercicio y aplicación de los recursos públicos federales, de los capitulo 1000, 2000, 3000, 4000 y 5000.</t>
-  </si>
-  <si>
-    <t>Artículo 74 fraccion VI y 79 de la Constitucion Politica de los Estados Unidos Mexicanos; fracciones II, VIII,IX, X, XI, XVI, XVIII y XXX; 6,9,14, fracciones I, III y IV; 17, fracciones I, VI, VII, VIII, XI, XII, XXVI, XXVII y XXVIII; 22, 23, 28, 29, 47, 48, 49, 58 y 67,  y demas relativos de Fiscalizacion y Rendicion de Cuentas de la Federacion; 8, el Presupuesto de Egresos de la Federacion para el ejercicio fiscal 2020, 2, 3, 12 fraccion III del Reglamento Interior de la Auditoria  Superior de la Federacion.</t>
-  </si>
-  <si>
-    <t>SFP/DSFCA/AOPS/2022-09-1517</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Subsidios Federales</t>
   </si>
   <si>
     <t>Dirección Administrativa 
@@ -304,102 +282,13 @@
 Departamento de contabilidad</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Departamento de contabilidad</t>
-  </si>
-  <si>
-    <t>03/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención a la observacion preliminar, lacual fue debidamente atendida y solventada, por lo que la auditoria mencionada ha concluido.</t>
-  </si>
-  <si>
-    <t>54E18CE1DC3F50A52ED09EBE5B4F67F0</t>
-  </si>
-  <si>
-    <t>1833</t>
-  </si>
-  <si>
-    <t>AEGF/0505/2022</t>
-  </si>
-  <si>
-    <t>Subisidios Federales para Organisos Descentralizados  Estatales</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de diciembre de 2022, derivado del  Acta de Presentacion de Resultados Finales y Observaciones Preliminares, el Colegio de Bachilleres del Estado de Tlaxcala, presentó a traves del oficio número D.A/1229/2022 y oficio D.A./1302/2022, el dia 23 de septiembre y 06 de Octubre del presente año respectivamente, la propuesta de solventación respectiva, encontrandose en analisis por el personal auditor habilitado.</t>
-  </si>
-  <si>
-    <t>E5BB54266FAECFFBFF2A7D6A7932586D</t>
-  </si>
-  <si>
-    <t>1821</t>
-  </si>
-  <si>
-    <t>AEGF/0192/2022</t>
-  </si>
-  <si>
-    <t>Participaciones Federales a Entidades Federativas</t>
-  </si>
-  <si>
-    <t>Participaciones Federales</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención a la solicitud de información adicional, asi mismo no se emitio resultado y/o observación para el Colegio de Bachilleres del Estado de Tlaxcala, por lo que la auditoria ha concluido.</t>
-  </si>
-  <si>
-    <t>F4A6971FB9E48DE15A2435ED82C06AA4</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>Oficio N. AEGF/0271/2022
-Orden de auditoría con motivo de la revisión de la Cuenta Pública 2021; se designa al personal auditor que se indica y se solicita información y documentación.</t>
-  </si>
-  <si>
-    <t>AEGF/0271/2022</t>
-  </si>
-  <si>
-    <t>Fondo de Aportaciones Múltiples FAM 2021</t>
-  </si>
-  <si>
-    <t>Ejercicio y aplicación de los recursos públicos federales, de los capitulo 5000 y 6000.</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala,  ha presentado la propuesta de solventacion respectiva, así como la justificacion y documentacion solicitada por la Secretaria de la Funcion Pública en el mes de Julio del ejercicio fiscal 2022, para llevar a cabo el proceso de la Presunta Responsabilidad Administrativa (PRAS) de los servidores públicos en turno, por lo que esta auditoria se encuentra culminada.</t>
-  </si>
-  <si>
-    <t>7D23CC6D33A41EE3515076D1BCA648DE</t>
-  </si>
-  <si>
-    <t>OFS/2792/2021</t>
-  </si>
-  <si>
     <t>Organo de fiscalización Superior del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>Orden de auditoría
-Oficio No. OFS/2792/2021</t>
-  </si>
-  <si>
     <t>Anexo I</t>
   </si>
   <si>
-    <t>Recursos de las Fuentes e Financiamiento, correspondiente al ejercicio fiscal 2021.</t>
-  </si>
-  <si>
     <t>Artículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
-  </si>
-  <si>
-    <t>OFS/1517/2022</t>
   </si>
   <si>
     <t>Recursos recaudados
@@ -407,50 +296,62 @@
 Remanentes de ejercicios anteriores y/o federales</t>
   </si>
   <si>
-    <t>(SA) Soluciones de aclaración.
-(PDP) Probable daño patrimonial.
-(PRAS) Promoción de resposabilidad administrativa sancionatoria.
-(R) Recomendaciones</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>https://www.ofstlaxcala.gob.mx/</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala,  atendió  la apertura de la auditoria  OFS/2792/2021 así como la integración de la información solicitada en el Anexo I, lo anterior para dar inicio a los trabajos de fiscalización, cabe señalar que durante este periodo se ha dado atención a la solicitud de información adicional  y solventación de observaciones emitidas por este Organo de Fiscalización Superior del Estado de Tlaxcala, por lo anterior esta auditoria se encuentra culminada.</t>
-  </si>
-  <si>
-    <t>B42435E8CB6C6517EB5151D235576505</t>
-  </si>
-  <si>
-    <t>Del 01/01/2022 al 31/12/2022</t>
-  </si>
-  <si>
-    <t>OFS/3651/2022</t>
+    <t>Dirección Administrativa
+Subdirección de Servicios Administrativos
+Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Del 01/01/2023 al 31/12/2023</t>
+  </si>
+  <si>
+    <t>OFS/2255/2023</t>
   </si>
   <si>
     <t>Orden de auditoría
-Oficio No. OFS/3651/2022</t>
-  </si>
-  <si>
-    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2022.</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala,  atendió  la apertura de la auditoria  OFS/3651/2022 así como la integración de la información solicitada en el Anexo I, lo anterior para dar inicio a los trabajos de fiscalización para el ejercicio fiscal 2022.</t>
+Oficio No. OFS/2255/2023</t>
+  </si>
+  <si>
+    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2023.</t>
+  </si>
+  <si>
+    <t>35870B6CD7E119F99F5D6447EE644A1B</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/10/2023</t>
+  </si>
+  <si>
+    <t>OFS/3248/2023</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>02/01/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de enero de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
+*En razon de lo antes mencionado con oficio número número D.G./032/2024 de fecha 22 de enero del 2024, se remite la propuesta de solventación respectiva, encontrandose a la espera de los resultados respectivos, motivo por lo cual no se encuentra acciones solventadas.</t>
   </si>
   <si>
     <t>Auditoría interna</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -546,6 +447,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -561,44 +465,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -626,14 +530,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -661,6 +582,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -672,175 +610,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -848,37 +762,38 @@
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="134.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="176.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="127.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="88" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="255" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="54.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="106.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="46" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="57.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="255" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -895,7 +810,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -910,7 +825,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -978,31 +893,34 @@
         <v>6</v>
       </c>
       <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>10</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>11</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>10</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>12</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1093,10 +1011,13 @@
       <c r="AE5" t="s">
         <v>43</v>
       </c>
+      <c r="AF5" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1128,672 +1049,204 @@
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
     </row>
-    <row r="7" spans="1:31" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="S8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="2" t="s">
+      <c r="X8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="AD8" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="AF8" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE12" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE13" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AE6"/>
+    <mergeCell ref="A6:AF6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1801,9 +1254,12 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G148">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G164" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_16</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X164" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>Hidden_223</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1811,18 +1267,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
